--- a/companies/nornickel_v2/data/excel/nornickel_v2_template_v3.xlsx
+++ b/companies/nornickel_v2/data/excel/nornickel_v2_template_v3.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mUSD</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -10262,42 +10262,42 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>opening_balance_mUSD</t>
+          <t>opening_balance_musd</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>committed_amount_mUSD</t>
+          <t>maturity_date</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>maturity_date</t>
+          <t>interest_rate</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>interest_rate</t>
+          <t>rate_type</t>
         </is>
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>rate_type</t>
+          <t>base_rate_factor</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>base_rate_factor</t>
+          <t>payment_frequency</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
-          <t>payment_frequency</t>
+          <t>amortization_profile</t>
         </is>
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>amortization_profile</t>
+          <t>callable_flag</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
@@ -10335,13 +10335,13 @@
       <c r="E2" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>0.12</v>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
@@ -10379,13 +10379,13 @@
       <c r="E3" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>0.12</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -10423,17 +10423,17 @@
       <c r="E4" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.035</v>
       </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>floating</t>
+          <t>cbr_key_rate</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -10471,17 +10471,17 @@
       <c r="E5" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.035</v>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>floating</t>
+          <t>cbr_key_rate</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -10519,13 +10519,13 @@
       <c r="E6" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.0575</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -10563,13 +10563,13 @@
       <c r="E7" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -10607,13 +10607,13 @@
       <c r="E8" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.073</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -10651,17 +10651,17 @@
       <c r="E9" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>0.02</v>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>floating</t>
+          <t>cbr_key_rate</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -10699,13 +10699,13 @@
       <c r="E10" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>0.04</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -10743,17 +10743,17 @@
       <c r="E11" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>floating</t>
+        </is>
+      </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>floating</t>
+          <t>cbr_key_rate</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">

--- a/companies/nornickel_v2/data/excel/nornickel_v2_template_v3.xlsx
+++ b/companies/nornickel_v2/data/excel/nornickel_v2_template_v3.xlsx
@@ -5144,86 +5144,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INCOME STATEMENT — canonical metrics</t>
+          <t>INCOME STATEMENT — all metrics from FS Excel (mUSD)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>db_metric</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>sign</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G2" s="6" t="n">
         <v>2011</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="6" t="n">
         <v>2012</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="I2" s="6" t="n">
         <v>2013</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="J2" s="6" t="n">
         <v>2014</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="K2" s="6" t="n">
         <v>2015</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="L2" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="6" t="n">
         <v>2017</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="6" t="n">
         <v>2018</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="6" t="n">
         <v>2019</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="6" t="n">
         <v>2020</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>2021</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="R2" s="6" t="n">
         <v>2022</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="S2" s="6" t="n">
         <v>2023</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="T2" s="6" t="n">
         <v>2024</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="U2" s="6" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -5246,126 +5250,100 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
         <v>14122</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>12366</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>11499</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>11869</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>8542</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>8259</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>9146</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>11670</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="O3" s="3" t="n">
         <v>13563</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="P3" s="3" t="n">
         <v>15545</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>17852</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" s="3" t="n">
         <v>16876</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>14409</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>12535</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="U3" s="3" t="n">
         <v>13763</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost of Sales</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>cogs</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Cost of Metal Sales</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>cost_metal_sales</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>-4967</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-5420</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-5545</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-4805</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-3165</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>-3633</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-3939</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>-4505</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-4499</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-4500</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-5057</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>-6103</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>-6344</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>-6221</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>-6920</v>
-      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Cost of Other Sales</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>gross_profit</t>
+          <t>cost_other_sales</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -5376,171 +5354,167 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>-4967</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-6367</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-6506</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-5674</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-3781</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-4141</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-4600</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-4505</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-4499</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-5057</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-6103</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-7032</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-6877</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>-7613</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n">
         <v>8329</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="H7" s="3" t="n">
         <v>5999</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="I7" s="3" t="n">
         <v>4993</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="J7" s="3" t="n">
         <v>6195</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="K7" s="3" t="n">
         <v>4761</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="L7" s="3" t="n">
         <v>4118</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M7" s="3" t="n">
         <v>4575</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="N7" s="3" t="n">
         <v>6543</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="O7" s="3" t="n">
         <v>8386</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="P7" s="3" t="n">
         <v>10481</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="Q7" s="3" t="n">
         <v>12049</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="R7" s="3" t="n">
         <v>9963</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="S7" s="3" t="n">
         <v>7377</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>5647</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="T7" s="3" t="n">
+        <v>5658</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>6150</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>sga</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n">
-        <v>-1180</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>-1614</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>-1389</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>-1465</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>-1560</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Distribution Expenses</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>distribution_expenses</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-828</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>-578</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-445</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-335</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-129</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>-111</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-75</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>-92</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-133</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>-167</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>-191</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>-261</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>-296</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>-419</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>-319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>Distribution Expenses</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>rnd</t>
+          <t>distribution_expenses</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -5551,66 +5525,138 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>828</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-578</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>-445</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>-130</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>-129</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>-75</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>-92</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>-133</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>-167</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>-191</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>-261</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>-296</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>-419</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>-319</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Other Operating Income</t>
+          <t>Administrative Expenses</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>other_operating_income</t>
+          <t>admin_expenses</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>636</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>755</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>848</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>-279</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>-841</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>-812</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>-554</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>-581</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>-788</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>-890</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>-938</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>-869</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>-989</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>-1353</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>-1093</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>-1046</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>-1241</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Other Operating Expense</t>
+          <t>SG&amp;A (total)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>other_operating_expense</t>
+          <t>sga</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -5633,19 +5679,31 @@
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n">
+        <v>-1180</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>-1614</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>-1389</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>-1465</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>-1560</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Asset Impairment</t>
+          <t>Other Operating Expenses</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>asset_impairment</t>
+          <t>other_operating_expenses</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -5657,64 +5715,70 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>243</v>
+        <v>90</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>841</v>
+        <v>175</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-24</v>
+        <v>-362</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>308</v>
+        <v>-95</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>48</v>
+        <v>-303</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>90</v>
+        <v>-2737</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>179</v>
+        <v>-1285</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>441</v>
+        <v>-678</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>319</v>
+        <v>-269</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>-178</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>-333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Depreciation (PPE)</t>
+          <t>Asset Impairment</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>depreciation_owned</t>
+          <t>asset_impairment</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -5722,60 +5786,66 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>761</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>789</v>
+        <v>15</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>881</v>
+        <v>243</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>805</v>
+        <v>279</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>506</v>
+        <v>66</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>557</v>
+        <v>-244</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>645</v>
+        <v>284</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>765</v>
+        <v>61</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>911</v>
+        <v>227</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>943</v>
+        <v>50</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>928</v>
+        <v>24</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1026</v>
+        <v>308</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1165</v>
+        <v>48</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1181</v>
+        <v>90</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1411</v>
+        <v>179</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>441</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Depreciation (RoU)</t>
+          <t>Depreciation (PPE)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>depreciation_rou</t>
+          <t>depreciation_owned</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -5788,29 +5858,61 @@
       </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>761</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>789</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>881</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>805</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>506</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>557</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>645</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>765</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>911</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>943</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>928</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>1026</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>1165</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>1181</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation (RoU)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>amortization</t>
+          <t>depreciation_rou</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -5821,51 +5923,23 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -5887,178 +5961,196 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
+        <v>665</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>673</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>761</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>789</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>881</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>805</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>506</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>557</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>645</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>765</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>911</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="P15" s="4" t="n">
         <v>943</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>928</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>1026</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>1165</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>1181</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>7209</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>7239</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="H16" s="3" t="n">
+        <v>4198</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>7209</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>7239</v>
+      </c>
+      <c r="K16" s="3" t="n">
         <v>4932</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="L16" s="3" t="n">
         <v>4198</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="M16" s="3" t="n">
         <v>5681</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="N16" s="3" t="n">
         <v>4296</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="O16" s="3" t="n">
         <v>3899</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="P16" s="3" t="n">
         <v>3995</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="Q16" s="3" t="n">
         <v>6231</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="R16" s="3" t="n">
         <v>7923</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="S16" s="3" t="n">
         <v>7651</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="T16" s="3" t="n">
         <v>10512</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="U16" s="3" t="n">
         <v>8697</v>
       </c>
-      <c r="Q16" s="4" t="n">
-        <v>6884</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>5196</v>
-      </c>
-      <c r="S16" s="4" t="n">
-        <v>5668</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
+        <v>3565</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6552</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>6235</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="H17" s="3" t="n">
         <v>3864</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="I17" s="3" t="n">
         <v>2476</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="J17" s="3" t="n">
         <v>4746</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="K17" s="3" t="n">
         <v>3506</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="L17" s="3" t="n">
         <v>3281</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="M17" s="3" t="n">
         <v>3123</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="N17" s="3" t="n">
         <v>5416</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="O17" s="3" t="n">
         <v>7036</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="P17" s="3" t="n">
         <v>6400</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="Q17" s="3" t="n">
         <v>9536</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="R17" s="3" t="n">
         <v>7581</v>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="S17" s="3" t="n">
         <v>5540</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="T17" s="3" t="n">
         <v>3574</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="U17" s="3" t="n">
         <v>3938</v>
       </c>
     </row>
@@ -6082,48 +6174,54 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-151</v>
+        <v>174</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-294</v>
+        <v>138</v>
       </c>
       <c r="G18" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-552</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>-376</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>-179</v>
-      </c>
-      <c r="I18" s="3" t="n">
+      <c r="J18" s="3" t="n">
+        <v>-213</v>
+      </c>
+      <c r="K18" s="3" t="n">
         <v>-326</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>-453</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>-535</v>
-      </c>
       <c r="L18" s="3" t="n">
+        <v>-153</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" s="3" t="n">
         <v>-580</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="O18" s="3" t="n">
         <v>-306</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="P18" s="3" t="n">
         <v>-879</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="Q18" s="3" t="n">
         <v>-279</v>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="R18" s="3" t="n">
         <v>-493</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="S18" s="3" t="n">
         <v>-567</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="T18" s="3" t="n">
         <v>-896</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="U18" s="3" t="n">
         <v>-934</v>
       </c>
     </row>
@@ -6146,49 +6244,51 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="O19" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="P19" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="S19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>171</v>
       </c>
     </row>
@@ -6226,11 +6326,13 @@
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Earnings from Investees</t>
+          <t>Earnings from Associates</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -6246,35 +6348,71 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>552</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>611</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>363</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Other Financial Income/Loss</t>
+          <t>Finance Costs Net</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>other_losses_gains_net</t>
+          <t>finance_costs_net</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -6296,16 +6434,18 @@
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>EBT</t>
+          <t>FX Gain/Loss</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ebt</t>
+          <t>fx_gain_loss</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -6316,96 +6456,132 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>-1594</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>-865</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>491</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>-1029</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>694</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>-1034</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-53</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-1512</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-343</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ebt</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>3306</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>6782</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>5646</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="H24" s="3" t="n">
         <v>3143</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="I24" s="3" t="n">
         <v>1330</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="J24" s="3" t="n">
         <v>2660</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="K24" s="3" t="n">
         <v>2244</v>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>3429</v>
-      </c>
-      <c r="K23" s="4" t="n">
+      <c r="L24" s="3" t="n">
+        <v>3276</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>2844</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="N24" s="3" t="n">
         <v>3902</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="O24" s="3" t="n">
         <v>7524</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="P24" s="3" t="n">
         <v>4579</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="Q24" s="3" t="n">
         <v>9285</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="R24" s="3" t="n">
         <v>7379</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="S24" s="3" t="n">
         <v>3534</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="T24" s="3" t="n">
         <v>2404</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="U24" s="3" t="n">
         <v>3286</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Current Tax</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>current_tax_expense</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Current Tax</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>deferred_tax_expense</t>
+          <t>current_tax_expense</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -6431,141 +6607,189 @@
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Tax Expense</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>tax_expense</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Deferred Tax</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>deferred_tax_expense</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>-1460</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-565</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>-660</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>-528</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>-745</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>-721</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-843</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>-1558</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>-945</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-2311</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-1525</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-664</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-589</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-816</v>
-      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>Tax Expense</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>tax_expense</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>802</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1548</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>-565</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>-660</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>-528</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-745</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>-721</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>-843</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>-1558</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>-945</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>-2311</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>-1525</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>-664</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>-589</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>-816</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C28" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E28" s="3" t="n">
+        <v>2651</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3089</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>3626</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="I28" s="3" t="n">
         <v>765</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="J28" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="K28" s="3" t="n">
         <v>1716</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="L28" s="3" t="n">
         <v>2531</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="M28" s="3" t="n">
         <v>2123</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="N28" s="3" t="n">
         <v>3059</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="O28" s="3" t="n">
         <v>5966</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="P28" s="3" t="n">
         <v>3634</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="Q28" s="3" t="n">
         <v>6974</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="R28" s="3" t="n">
         <v>5854</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="S28" s="3" t="n">
         <v>2870</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="T28" s="3" t="n">
         <v>1815</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="U28" s="3" t="n">
         <v>2470</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6576,93 +6800,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BALANCE SHEET — canonical metrics</t>
+          <t>BALANCE SHEET — all metrics from FS Excel (mUSD)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>db_metric</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>sign</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G2" s="6" t="n">
         <v>2011</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="6" t="n">
         <v>2012</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="I2" s="6" t="n">
         <v>2013</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="J2" s="6" t="n">
         <v>2014</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="K2" s="6" t="n">
         <v>2015</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="L2" s="6" t="n">
         <v>2016</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="6" t="n">
         <v>2017</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="6" t="n">
         <v>2018</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="6" t="n">
         <v>2019</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="6" t="n">
         <v>2020</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>2021</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="R2" s="6" t="n">
         <v>2022</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="S2" s="6" t="n">
         <v>2023</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="T2" s="6" t="n">
         <v>2024</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="U2" s="6" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Cash &amp; Equivalents</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6679,48 +6907,54 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
+        <v>3632</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>5405</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>1627</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>1037</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>1621</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>2793</v>
-      </c>
       <c r="I3" s="3" t="n">
-        <v>4054</v>
+        <v>594</v>
       </c>
       <c r="J3" s="3" t="n">
+        <v>436</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>3325</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>852</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>1388</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="O3" s="3" t="n">
         <v>2784</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="P3" s="3" t="n">
         <v>5191</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>5547</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" s="3" t="n">
         <v>1882</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>2139</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>1822</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="U3" s="3" t="n">
         <v>2106</v>
       </c>
     </row>
@@ -6758,6 +6992,8 @@
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -6779,48 +7015,54 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
+        <v>978</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>1032</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>1063</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>633</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>327</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>362</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>537</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>468</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>764</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>1374</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="U5" s="3" t="n">
         <v>1152</v>
       </c>
     </row>
@@ -6844,60 +7086,66 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2246</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>2623</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>3197</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>2955</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>1726</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>1698</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>1912</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>2689</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>2280</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="O6" s="3" t="n">
         <v>2475</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="P6" s="3" t="n">
         <v>2192</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="Q6" s="3" t="n">
         <v>3026</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" s="3" t="n">
         <v>4945</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>3817</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>3114</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="U6" s="3" t="n">
         <v>3894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Other Current Assets</t>
+          <t>Advances &amp; Prepaid</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>other_current_assets</t>
+          <t>advances_prepaid</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -6908,2194 +7156,7 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Total Current Assets</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>total_current_assets</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>PPE Net</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>ppe_net</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>9585</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>11927</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>11222</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>7011</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>6392</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>9306</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>10960</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>9934</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>11993</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>10762</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>12699</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>16264</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>15181</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>15261</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>22091</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>RoU Asset</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>rou_asset</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Intangibles</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>intangibles</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>222</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>302</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>238</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>goodwill</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Investments in Associates</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>investments_in_associates</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>LT Investments &amp; Receivables</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>investments_lt</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>407</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>329</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>DTA</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>dta</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>755</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>335</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>328</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Other Non-Current Assets</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>other_nca</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Total Non-Current Assets</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>total_non_current_assets</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>total_assets</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>18912</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>20974</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>18781</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>13149</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>13371</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>16523</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>16635</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>15251</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>19474</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>20706</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>23435</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>25795</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>23580</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>23170</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>31256</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Short-Term Debt</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>short_term_debt</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>2526</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>1032</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>652</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>1124</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>579</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>813</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>209</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>1087</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>1610</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>4295</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>4335</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>2834</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>3109</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>accounts_payable</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>543</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>696</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>619</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>908</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1010</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>1613</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>783</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>1551</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>1706</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>1427</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>2224</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>1381</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>1273</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>1209</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>1669</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Taxes Payable</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>taxes_payable</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>358</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Interest Payable</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>interest_payable</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Payroll &amp; Benefits Payable</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>payroll_payable</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Lease Liab Current</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>lease_liab_current</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>other_cl</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>total_current_liabilities</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>long_term_debt</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>2401</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2497</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>5173</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>5678</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>7142</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>7276</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>8212</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>8208</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>8533</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>9622</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>8616</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>7189</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>5377</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>7112</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>7587</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>DTL</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>dtl</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>651</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>573</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>382</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>216</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>205</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>355</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>407</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>385</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>415</v>
-      </c>
-      <c r="Q28" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>381</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>employee_benefits</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Lease Liab Non-Current</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>lease_liab_noncurrent</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n">
-        <v>178</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q30" s="4" t="n">
-        <v>466</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>381</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Other Non-Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>other_ncl</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Total Non-Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>total_non_current_liabilities</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>total_liabilities</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>7690</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>8034</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>9031</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>8356</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>11110</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>12627</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>11977</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>11778</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>15187</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16031</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>18647</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>17228</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>15985</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>15073</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>17811</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Share Capital</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>APIC / Share Premium</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>apic</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>1511</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>1511</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>1254</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>1218</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>1212</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>1212</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>1212</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Treasury Stock</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>treasury_stock</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>retained_earnings</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>19123</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>20353</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>9589</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>8295</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>6523</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>7340</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>7557</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>7306</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>7452</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>8290</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>8184</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>10448</v>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v>11324</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>12638</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>14974</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>AOCI</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>aoci</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-848</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>-349</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>-1230</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>-4787</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>-5348</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>-4778</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>-4490</v>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>-5343</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>-4899</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>-5521</v>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>-5415</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>-4541</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>-6146</v>
-      </c>
-      <c r="R38" s="4" t="n">
-        <v>-6979</v>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>-4876</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>NCI</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>nci</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>331</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>474</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>646</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>1442</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>1199</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>1220</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>total_equity</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>11222</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>12940</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>9750</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>4793</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>2261</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>3896</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>4658</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>3473</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>4287</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>4675</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>4788</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>8567</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>7595</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>8097</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>13445</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CASH FLOW STATEMENT — canonical metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>excel_metric</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>db_metric</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>sign</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>2015</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Net Income (CFO)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>cfo_net_income</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>5165</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>3143</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1330</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>2660</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>2244</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>3276</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>2844</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>3902</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>7524</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>4579</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>9285</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>7379</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>3534</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>2404</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>depreciation</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>depreciation</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>amortization</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>amortization</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Total D&amp;A</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>total_da</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>total_da</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>762</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>789</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>881</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>805</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>506</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>557</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>645</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>765</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>911</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>943</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>928</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1026</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>1165</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1181</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Deferred Tax</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>deferred_tax</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>deferred_tax</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
@@ -9111,271 +7172,450 @@
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
+      <c r="U7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Stock Compensation</t>
+          <t>Other Current Assets</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>stock_compensation</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>stock_compensation</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
+          <t>other_current_assets</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Impairment</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>impairment</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>impairment</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>total_current_assets</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
+      <c r="E9" s="3" t="n">
+        <v>8376</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>10158</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>6569</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>6814</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>5898</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>5249</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>6408</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>5846</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>4526</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>4554</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>6575</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>8559</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>9870</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>8403</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>7342</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>6845</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>7732</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Change in WC</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>change_in_wc</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>change_in_wc</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PPE Net</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ppe_net</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
+      <c r="E10" s="3" t="n">
+        <v>11017</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>9153</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>9585</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>11927</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>11222</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>7011</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>6392</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>9306</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>10960</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>9934</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>11993</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>10762</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>12699</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>16264</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>15181</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>15261</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>22091</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Change in Receivables</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>change_ar</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>change_ar</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+          <t>goodwill</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Change in Inventory</t>
+          <t>Intangibles</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>change_inv</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>change_inv</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+          <t>intangibles</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Change in Payables</t>
+          <t>Investments in Associates</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>change_ap</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>change_ap</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
+          <t>investments_in_associates</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>515</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>407</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>351</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Other CFO</t>
+          <t>Other Financial Assets (NCA)</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>other_cfo</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>other_cfo</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
+          <t>other_financial_assets_nca</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
@@ -9391,25 +7631,2909 @@
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>DTA</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>dta</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>755</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Other NCA</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>other_nca</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>1013</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>292</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Total Non-Current Assets</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>total_non_current_assets</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>14352</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>10935</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>12343</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>14160</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>12289</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>7464</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>6746</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>10677</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>12109</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>10697</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>12899</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>12147</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>13565</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>17392</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>16238</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>16325</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>23524</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>total_assets</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>22760</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>23909</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>18912</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>20974</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>18781</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>13149</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>13371</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>16523</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>16635</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>15251</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>19474</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>20706</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>23435</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>25795</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>23580</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>23170</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>31256</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>short_term_debt</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2972</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1236</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2754</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>2526</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>652</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>813</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>1087</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>1610</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>4295</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>4335</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>2834</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>accounts_payable</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>486</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>599</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>543</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>696</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>619</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>1613</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>783</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1551</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>1706</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1427</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>2224</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>1381</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>1273</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Lease Liab Current</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>lease_liab_current</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>income_tax_payable</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Other Taxes Payable</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>other_taxes_payable</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Provisions (Current)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>provisions_current</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>2162</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>employee_benefits</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>498</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>417</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>585</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>444</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>total_current_liabilities</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>3302</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>3240</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1652</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1583</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>2139</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>2194</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>1609</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1801</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>2873</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>1856</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>3932</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>5888</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>5669</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>4173</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>4984</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>long_term_debt</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2345</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1561</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>2401</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>2497</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>5173</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>5678</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>7142</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>7276</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>8212</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>8208</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8533</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>9622</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>8616</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>7189</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>5377</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>7112</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Lease Liab Non-Current</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>lease_liab_noncurrent</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="S28" s="4" t="n">
+        <v>466</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>DTL</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>dtl</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>729</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>651</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>573</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>415</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Provisions (Non-Current)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>provisions</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>901</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>716</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>274</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>441</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>636</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>894</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>916</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>689</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>881</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Social Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>social_liabilities</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>633</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>613</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Other NCL</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>other_ncl</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Total Non-Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>total_non_current_liabilities</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>3052</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>3070</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>5555</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>5894</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>7347</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>7631</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>8619</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>8593</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>8593</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>9665</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>8867</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>7794</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>5985</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7874</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>8941</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>total_liabilities</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>7690</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>8034</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>9031</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>8356</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>11110</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>12627</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>11977</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>11778</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>15187</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>16031</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>18647</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>17228</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>15985</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>15073</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>17811</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>share_capital</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Share Premium</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>apic</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1511</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1511</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1511</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>1254</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>1218</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>treasury_stock</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>-2719</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>-1237</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-8692</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-349</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>-1230</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>-196</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>-305</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>AOCI / Translation Reserves</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>aoci</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>-604</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-848</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>-349</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>-4787</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>-5348</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>-4778</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>-4490</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>-5343</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>-4899</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>-5521</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>-5415</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>-4541</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>-6146</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>-6979</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>-4876</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>retained_earnings</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>15600</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>17744</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>19123</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>20353</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>9589</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>8295</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>6523</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>7340</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>7557</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>7306</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>7452</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>8290</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>8184</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>10448</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>11324</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>12638</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14974</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>NCI</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>nci</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>598</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>474</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>646</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>1442</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>1199</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>1220</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>total_equity</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>14755</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>17974</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>11222</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>12940</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>9750</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>4793</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>2261</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>3896</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>4658</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>3473</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>4287</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>4675</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>4788</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>8567</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>7595</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>8097</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>13445</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASH FLOW STATEMENT — all metrics from FS Excel (mUSD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>excel_metric</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>db_metric</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>sign</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>2017</v>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>2018</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Net Income / EBT (CFO)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ebt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ebt</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3487</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4631</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>5165</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>3143</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>2660</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>2244</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>3276</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>2844</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>3902</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>7524</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>4579</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>9285</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>7379</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>3534</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>2404</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>total_da</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>total_da</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>817</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>803</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>762</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>881</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>805</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>557</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>765</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>911</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>943</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1026</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1165</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1181</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Impairment</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>impairment</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>impairment</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-175</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>841</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>-24</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>441</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Loss on Disposal PPE</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>loss_on_disposal</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>loss_on_disposal</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Share of Associates</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>share_of_associates</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>share_of_associates</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>-50</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Finance Costs Net</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>finance_costs_net_cf</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>finance_costs_net</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>458</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>806</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>493</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>567</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>896</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FX Gain/Loss</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>fx_gain_loss_cf</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>fx_gain_loss</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>-214</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1594</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>865</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>-491</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>-159</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>1029</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>-694</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1034</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>-251</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>1512</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Change in Inventory</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>change_inventory</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>change_inventory</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-425</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-508</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>-409</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>-340</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>-751</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>-346</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>-796</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>-1693</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>-185</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Change in Receivables</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>change_ar</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>change_ar</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-480</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-155</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>237</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>-174</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>-122</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>-161</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>-347</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>-610</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Interest Paid</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>interest_paid</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>interest_paid</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>-230</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>-229</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>-259</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>-376</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>-591</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>-642</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>-551</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>-497</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>-510</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>-315</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>-599</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>-791</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>-1468</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>-1700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Taxes Paid</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>taxes_paid</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>taxes_paid</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-357</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>-1586</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>-1926</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>-859</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>-585</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>-825</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>-672</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>-530</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>-670</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>-787</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>-1910</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>-1304</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>-2211</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>-1127</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>-1164</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>-338</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>-353</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>CFO Total</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>cfo_total</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>cfo_total</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3401</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>5514</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>4702</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>3434</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>4344</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>5947</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>3705</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>3511</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>1763</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>6493</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>6009</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>8288</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>7042</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>4586</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>5728</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>4433</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>6018</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CFO Total</t>
+          <t>CapEx</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>cfo_total</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>cfo_total</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -9417,215 +10541,265 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>4702</v>
+        <v>-1061</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3434</v>
+        <v>-1728</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>4344</v>
+        <v>-2201</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>5947</v>
+        <v>-2692</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3705</v>
+        <v>-1970</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>3510.71</v>
+        <v>-1277</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1762.62</v>
+        <v>-1626</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>6493</v>
+        <v>-1667</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>6009.47</v>
+        <v>-1940</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>8287.879999999999</v>
+        <v>-1480</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>7042</v>
+        <v>-1262</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>4586</v>
+        <v>-1686</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>5728</v>
+        <v>-2683</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4433</v>
+        <v>-4227</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>6018</v>
+        <v>-2988</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>-2386</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>-2569</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>CapEx</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>capex</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>capex</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Acquisitions</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>acquisitions</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>acquisitions</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-2201</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-2692</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-1970</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>-1277</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>-1626</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>-1667</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>-1940</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>-1480</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>-1262</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>-1686</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>-2683</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-4227</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-2988</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-2386</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>-2569</v>
-      </c>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4" t="n"/>
+      <c r="V16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CapEx Intangibles</t>
+          <t>Disposal Proceeds</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>capex_intangibles</t>
+          <t>disposal_proceeds</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>capex_intangibles</t>
+          <t>disposal_proceeds</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>mUSD</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CFI Total</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>cfi_total</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>cfi_total</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Acquisitions</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>acquisitions</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>acquisitions</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
+      <c r="F18" s="3" t="n">
+        <v>-468</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-1443</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-1876</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>-2914</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>-1738</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>-1222</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>-1920</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>-1936</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>-1562</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>-1120</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>-1648</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>-2638</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>-4149</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>-3042</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>-2575</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>-2532</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Proceeds from Asset Sales</t>
+          <t>Debt Issuance</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>proceeds_asset_sales</t>
+          <t>debt_issuance</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>proceeds_asset_sales</t>
+          <t>debt_issuance</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -9636,40 +10810,76 @@
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
+      <c r="F19" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>628</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>3694</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>2478</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>6001</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1916</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>3192</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>936</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>4233</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>2173</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>3212</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>2903</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>9104</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>5569</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>7273</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>12598</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Other CFI</t>
+          <t>Debt Repayments</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>other_cfi</t>
+          <t>debt_repayments</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>other_cfi</t>
+          <t>debt_repayments</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -9691,95 +10901,103 @@
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>CFI Total</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>cfi_total</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>cfi_total</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dividends Paid</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>dividends_paid</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>dividends_paid</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-1876</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-2914</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>-1738</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>-1222</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>-1300</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-1920</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>-1936</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>-1562</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-1120</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-1648</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-2638</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-4149</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-3042</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>-2575</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-2532</v>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-1208</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>-1234</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>-960</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>-2989</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>-3281</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-2859</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>-1232</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>-2971</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>-3369</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>-4166</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>-4165</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>-2198</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>-6196</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="U21" s="4" t="n">
+        <v>-1480</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Debt Issued</t>
+          <t>Dividends NCI</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>debt_issued</t>
+          <t>dividends_nci</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>debt_issued</t>
+          <t>dividends_nci</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -9801,21 +11019,23 @@
       <c r="R22" s="4" t="n"/>
       <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4" t="n"/>
+      <c r="V22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Debt Repaid</t>
+          <t>Lease Payments</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>debt_repaid</t>
+          <t>lease_payments</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>debt_repaid</t>
+          <t>lease_payments</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -9831,105 +11051,137 @@
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="4" t="n"/>
+      <c r="K23" s="4" t="n">
+        <v>-3281</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>-45</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-46</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-50</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-45</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Dividends Paid</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>dividends_paid</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>dividends_paid</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>CFF Total</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>cff_total</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>cff_total</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>mUSD</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>-1234</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>-960</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>-2989</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>-3281</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>-2859</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>-1232</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>-2971</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>-3369</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>-4166</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>-4165</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>-2198</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>-6196</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>-1480</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>-20</v>
+      <c r="F24" s="3" t="n">
+        <v>-1187</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-2034</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-6644</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-1164</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>-1975</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-2979</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-998</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>-2399</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>-2237</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-4304</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>-3623</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>-4332</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>-4047</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>-5064</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>-2404</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>-2042</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>-3247</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Share Buyback</t>
+          <t>FX Effect</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>share_buyback</t>
+          <t>fx_effect</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>share_buyback</t>
+          <t>fx_effect</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -9951,21 +11203,23 @@
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4" t="n"/>
+      <c r="V25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Share Issuance</t>
+          <t>Net Change in Cash</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>share_issuance</t>
+          <t>net_change_cash</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>share_issuance</t>
+          <t>net_change_cash</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
@@ -9991,25 +11245,27 @@
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4" t="n"/>
+      <c r="V26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Lease Payments</t>
+          <t>Cash Beginning</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>lease_payments</t>
+          <t>cash_beginning</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>lease_payments</t>
+          <t>cash_beginning</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -10031,21 +11287,23 @@
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4" t="n"/>
+      <c r="V27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Other CFF</t>
+          <t>Cash Ending</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>other_cff</t>
+          <t>cash_ending</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>other_cff</t>
+          <t>cash_ending</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
@@ -10071,161 +11329,10 @@
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
       <c r="T28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>CFF Total</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>cff_total</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>cff_total</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-6644</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>-1164</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>-1975</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>-2979</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>-998</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>-2399</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>-2237</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>-4304</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>-3623</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>-4332</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>-4047</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>-5064</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>-2404</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>-2042</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>-3247</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>FX Effect</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>fx_effect</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>fx_effect</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Net Change in Cash</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>net_change_cash</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>net_change_cash</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>mUSD</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-      <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
